--- a/tasks/finalpool/fetch-email-gcal-scheduler-excel-word/groundtruth_workspace/Scheduler_Report.xlsx
+++ b/tasks/finalpool/fetch-email-gcal-scheduler-excel-word/groundtruth_workspace/Scheduler_Report.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,33 +457,97 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Category A</t>
+          <t>Customer Support</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>92</v>
+      </c>
+      <c r="C2" t="n">
         <v>100</v>
       </c>
-      <c r="C2" t="n">
-        <v>95</v>
-      </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Category B</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="C3" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>-10</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Human Resources</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>88</v>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>118</v>
+      </c>
+      <c r="C5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>74</v>
+      </c>
+      <c r="C6" t="n">
+        <v>100</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-26</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>110</v>
+      </c>
+      <c r="C7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -497,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,21 +579,81 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Total_Items</t>
+          <t>Total_Departments</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Avg_Gap</t>
+          <t>Average_Internal_Value</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-2.5</v>
+        <v>97.83</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Average_External_Benchmark</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Average_Gap</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>-2.17</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Departments_Exceeding_Benchmark</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Departments_Below_Benchmark</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Largest_Positive_Gap</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Largest_Negative_Gap</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>-26</v>
       </c>
     </row>
   </sheetData>
@@ -543,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -564,7 +688,57 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Review Category B</t>
+          <t>Operations: gap -26 vs benchmark — investigate and improve scheduling efficiency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Human Resources: gap -12 vs benchmark — investigate and improve scheduling efficiency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Customer Support: gap -8 vs benchmark — investigate and improve scheduling efficiency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Finance: at/above benchmark — maintain current scheduling practices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Marketing: at/above benchmark — maintain current scheduling practices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sales: at/above benchmark — maintain current scheduling practices.</t>
         </is>
       </c>
     </row>
